--- a/docs/01-案例清单.xlsx
+++ b/docs/01-案例清单.xlsx
@@ -445,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1034,6 +1034,168 @@
       </c>
       <c r="G21" s="2" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.datastructures.lists.SortedLinkedList</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>SortedLinkedListTest.java</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>有序链表，数据结构类，自带测试 24 个（新增类型：数据结构-链表）</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.compression.LZ78</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>136</v>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>LZ78Test.java</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>LZ78 压缩算法，自带测试 26 个（新增类型：压缩）</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.dynamicprogramming.DamerauLevenshteinDistance</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>DamerauLevenshteinDistanceTest.java</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>编辑距离变体，动态规划，自带测试 22 个（新增类型：DP）</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.bitmanipulation.BitRotate</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>BitRotateTest.java</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>位循环移位，自带测试 20 个（新增类型：位运算）</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.ciphers.PermutationCipher</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>194</v>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>PermutationCipherTest.java</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>置换密码，自带测试 23 个（新增类型：加密）</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>com.thealgorithms.datastructures.stacks.StackOfLinkedList</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>135</v>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>StackOfLinkedListTest.java</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>链表实现栈，自带测试 18 个（新增类型：栈）</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1045,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1137,7 +1299,6 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" s="3" t="inlineStr"/>
     </row>
     <row r="9">
@@ -1165,7 +1326,6 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
@@ -1181,7 +1341,6 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
           <t>① 原 #20 类名 QuadraticEquationSolve 少了结尾 r，已更正为 QuadraticEquationSolver</t>
@@ -1189,7 +1348,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
           <t>② 原 #18 RomanNumeralUtil 无自带测试，已换为 misc.MedianOfRunningArray</t>
@@ -1197,7 +1355,6 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
           <t>③ 原 #13 QuickSort、#14 MergeSort 的测试继承自 SortingAlgorithmTest（父类 38 个方法），规模不可比，已换为 InsertionSort / BubbleSort（自带测试独立编写）</t>
@@ -1205,7 +1362,6 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
           <t>④ 为改善类型分布，SumOfDigits 换为 searches.JumpSearch；数学类由 10 个降至 8 个</t>
@@ -1213,7 +1369,6 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
           <t>⑤ 主代码行数与自带测试方法数全部由源码实测重算，不再手填</t>
@@ -1221,10 +1376,49 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
       <c r="B18" s="3" t="inlineStr">
         <is>
           <t>⑥ 「认领人」一列留空，由组员 5、6 各认领 10 个后填写</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>扩充记录（10-23）</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>老师同意可增加案例，由 20 个扩至 26 个</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>新增 6 个案例，覆盖原来没有的类型：链表、压缩、动态规划、位运算、加密、栈</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>新增案例的自带测试都很强（18–26 个方法），可降低"专挑基线弱的案例"这一质疑</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>组员5 加 3 个（序号 21、22、23），组员6 加 3 个（序号 24、25、26）</t>
         </is>
       </c>
     </row>

--- a/docs/01-案例清单.xlsx
+++ b/docs/01-案例清单.xlsx
@@ -519,7 +519,11 @@
           <t>数学类基础案例，逻辑简单但边界条件丰富，适合做代表性样例</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -546,7 +550,11 @@
           <t>经典递推/循环算法，适合观察循环与边界值覆盖</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -573,7 +581,11 @@
           <t>质数判定，边界条件多，适合观察正确性与异常处理</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -600,7 +612,11 @@
           <t>筛法是经典素数生成方法，循环与数组操作多</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -627,7 +643,11 @@
           <t>二分查找是核心搜索算法，分支条件明显</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -654,7 +674,11 @@
           <t>线性搜索简单常见，适合作为基础搜索对照</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -681,7 +705,11 @@
           <t>插值查找比二分更复杂，适合中等难度对照</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -708,7 +736,11 @@
           <t>KMP 是经典匹配算法，失败分支丰富</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -735,7 +767,11 @@
           <t>字符串基础案例，代码长度适中，稳定可复现</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -762,7 +798,11 @@
           <t>回文既经典又有边界条件，字符串代表案例</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -789,7 +829,11 @@
           <t>单词统计逻辑简单稳定，轻量级代表案例</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -816,7 +860,11 @@
           <t>最长公共前缀，测试场景可控</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -843,7 +891,11 @@
           <t>【替换 QuickSort】排序类且自带测试为独立编写（12 个方法），不继承公共父类</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>组员5</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -870,7 +922,11 @@
           <t>【替换 MergeSort】同上，自带测试独立编写（10 个方法）</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -897,7 +953,11 @@
           <t>行列式计算，递归展开与边界情况多</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -924,7 +984,11 @@
           <t>数论算法，分支和边界条件丰富</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -951,7 +1015,11 @@
           <t>【替换 RomanNumeralUtil】原类无自带测试；misc 类，自带测试 17 个，补足非数学类型</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -978,7 +1046,11 @@
           <t>【修正拼写】二次方程求解，分支与边界明显</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -1005,7 +1077,11 @@
           <t>数字求和，简单稳定，数学基础案例</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
@@ -1032,7 +1108,11 @@
           <t>【替换 SumOfDigits】跳跃搜索，自带测试 10 个，搜索类代表</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -1059,7 +1139,11 @@
           <t>有序链表，数据结构类，自带测试 24 个（新增类型：数据结构-链表）</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -1086,7 +1170,11 @@
           <t>LZ78 压缩算法，自带测试 26 个（新增类型：压缩）</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -1113,7 +1201,11 @@
           <t>编辑距离变体，动态规划，自带测试 22 个（新增类型：DP）</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
@@ -1140,7 +1232,11 @@
           <t>位循环移位，自带测试 20 个（新增类型：位运算）</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
@@ -1167,7 +1263,11 @@
           <t>置换密码，自带测试 23 个（新增类型：加密）</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
@@ -1194,7 +1294,11 @@
           <t>链表实现栈，自带测试 18 个（新增类型：栈）</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>组员6</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1383,7 +1487,6 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
       <c r="B19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
@@ -1399,7 +1502,6 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
           <t>新增 6 个案例，覆盖原来没有的类型：链表、压缩、动态规划、位运算、加密、栈</t>
@@ -1407,7 +1509,6 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
           <t>新增案例的自带测试都很强（18–26 个方法），可降低"专挑基线弱的案例"这一质疑</t>
@@ -1415,7 +1516,6 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
           <t>组员5 加 3 个（序号 21、22、23），组员6 加 3 个（序号 24、25、26）</t>

--- a/docs/01-案例清单.xlsx
+++ b/docs/01-案例清单.xlsx
@@ -1518,7 +1518,7 @@
     <row r="23">
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>组员5 加 3 个（序号 21、22、23），组员6 加 3 个（序号 24、25、26）</t>
+          <t>认领方式：序号 1-13 由组员5 负责，序号 14-26 由组员6 负责（各 13 个）</t>
         </is>
       </c>
     </row>
